--- a/vazby_znacek.xlsx
+++ b/vazby_znacek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petr.hirsal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vyvoj\dlazdice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99182AA0-ED39-437D-90E5-1C92E263F348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0256B98C-9AD9-42B4-A829-37EB79A90AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28605" yWindow="2430" windowWidth="28800" windowHeight="11295" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
+    <workbookView xWindow="-27675" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2553" uniqueCount="2527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="2569">
   <si>
     <t>name</t>
   </si>
@@ -7617,6 +7617,132 @@
   </si>
   <si>
     <t>Panastat</t>
+  </si>
+  <si>
+    <t>ID:ZN0447</t>
+  </si>
+  <si>
+    <t>severka</t>
+  </si>
+  <si>
+    <t>Severka</t>
+  </si>
+  <si>
+    <t>ID:ZN0436</t>
+  </si>
+  <si>
+    <t>mizon</t>
+  </si>
+  <si>
+    <t>MIZON</t>
+  </si>
+  <si>
+    <t>ID:ZN0446</t>
+  </si>
+  <si>
+    <t>jawhara</t>
+  </si>
+  <si>
+    <t>Jawhara</t>
+  </si>
+  <si>
+    <t>ID:ZN0448</t>
+  </si>
+  <si>
+    <t>pd</t>
+  </si>
+  <si>
+    <t>Afnan</t>
+  </si>
+  <si>
+    <t>ID:ZN0450</t>
+  </si>
+  <si>
+    <t>bouncibles</t>
+  </si>
+  <si>
+    <t>Bouncibles</t>
+  </si>
+  <si>
+    <t>ID:ZN0451</t>
+  </si>
+  <si>
+    <t>axis-y</t>
+  </si>
+  <si>
+    <t>AXIS-Y</t>
+  </si>
+  <si>
+    <t>ID:ZN0452</t>
+  </si>
+  <si>
+    <t>breakout-aid</t>
+  </si>
+  <si>
+    <t>Breakout+aid</t>
+  </si>
+  <si>
+    <t>ID:ZN0449</t>
+  </si>
+  <si>
+    <t>lattafa</t>
+  </si>
+  <si>
+    <t>Lattafa</t>
+  </si>
+  <si>
+    <t>ID:ZN0453</t>
+  </si>
+  <si>
+    <t>reparex</t>
+  </si>
+  <si>
+    <t>Reparex</t>
+  </si>
+  <si>
+    <t>ID:115851</t>
+  </si>
+  <si>
+    <t>tena</t>
+  </si>
+  <si>
+    <t>Tena</t>
+  </si>
+  <si>
+    <t>ID:ZN0454</t>
+  </si>
+  <si>
+    <t>childs-farm</t>
+  </si>
+  <si>
+    <t>Childs Farm</t>
+  </si>
+  <si>
+    <t>ID:ZN0455</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>ID:ZN0457</t>
+  </si>
+  <si>
+    <t>biscolata-mood</t>
+  </si>
+  <si>
+    <t>Biscolata MOOD</t>
+  </si>
+  <si>
+    <t>ID:ZN0458</t>
+  </si>
+  <si>
+    <t>yenkee</t>
+  </si>
+  <si>
+    <t>Yenkee</t>
   </si>
 </sst>
 </file>
@@ -8463,7 +8589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDB66AD-1FF0-4104-BCB9-E546CFC91809}">
-  <dimension ref="A1:C851"/>
+  <dimension ref="A1:C865"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -17832,6 +17958,160 @@
         <v>2526</v>
       </c>
     </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B852" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C852" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B853" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C853" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B854" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C854" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B855" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C855" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B856" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C856" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B857" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C857" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B858" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C858" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B859" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C859" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B860" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C860" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B861" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C861" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B862" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C862" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B863" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C863" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B864" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C864" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C865" t="s">
+        <v>2568</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/vazby_znacek.xlsx
+++ b/vazby_znacek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vyvoj\dlazdice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petr.hirsal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C954E663-D833-4571-8F41-C7072D9F255A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56072468-8BD2-494E-A85C-45D99A339258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27675" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
+    <workbookView xWindow="4710" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="2574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="2630">
   <si>
     <t>name</t>
   </si>
@@ -7758,6 +7758,174 @@
   </si>
   <si>
     <t>Eco-power</t>
+  </si>
+  <si>
+    <t>ID:ZN0459</t>
+  </si>
+  <si>
+    <t>iconique</t>
+  </si>
+  <si>
+    <t>ICONIQUE</t>
+  </si>
+  <si>
+    <t>ID:ZN0460</t>
+  </si>
+  <si>
+    <t>trimay</t>
+  </si>
+  <si>
+    <t>TRIMAY</t>
+  </si>
+  <si>
+    <t>ID:ZN0461</t>
+  </si>
+  <si>
+    <t>natura-hustopece</t>
+  </si>
+  <si>
+    <t>ID:ZN0430</t>
+  </si>
+  <si>
+    <t>brainmax</t>
+  </si>
+  <si>
+    <t>BrainMax</t>
+  </si>
+  <si>
+    <t>ID:ZN0462</t>
+  </si>
+  <si>
+    <t>nekupto</t>
+  </si>
+  <si>
+    <t>Nekupto</t>
+  </si>
+  <si>
+    <t>ID:ZN0463</t>
+  </si>
+  <si>
+    <t>z-trade</t>
+  </si>
+  <si>
+    <t>Z-Trade</t>
+  </si>
+  <si>
+    <t>ID:ZN0464</t>
+  </si>
+  <si>
+    <t>dryope</t>
+  </si>
+  <si>
+    <t>DRYOPE</t>
+  </si>
+  <si>
+    <t>ID:ZN0465</t>
+  </si>
+  <si>
+    <t>kitchisimo</t>
+  </si>
+  <si>
+    <t>Kitchisimo</t>
+  </si>
+  <si>
+    <t>ID:ZN0466</t>
+  </si>
+  <si>
+    <t>cegeco</t>
+  </si>
+  <si>
+    <t>Cegeco</t>
+  </si>
+  <si>
+    <t>ID:ZN0467</t>
+  </si>
+  <si>
+    <t>sama</t>
+  </si>
+  <si>
+    <t>Sama</t>
+  </si>
+  <si>
+    <t>ID:ZN0072</t>
+  </si>
+  <si>
+    <t>keeper</t>
+  </si>
+  <si>
+    <t>Keeper</t>
+  </si>
+  <si>
+    <t>ID:ZN0469</t>
+  </si>
+  <si>
+    <t>magic-studio</t>
+  </si>
+  <si>
+    <t>Magic Studio</t>
+  </si>
+  <si>
+    <t>ID:132657</t>
+  </si>
+  <si>
+    <t>jelinek</t>
+  </si>
+  <si>
+    <t>Jelínek</t>
+  </si>
+  <si>
+    <t>ID:ZN0470</t>
+  </si>
+  <si>
+    <t>forestina</t>
+  </si>
+  <si>
+    <t>FORESTINA</t>
+  </si>
+  <si>
+    <t>ID:ZN0471</t>
+  </si>
+  <si>
+    <t>andel-prerov</t>
+  </si>
+  <si>
+    <t>Anděl Přerov</t>
+  </si>
+  <si>
+    <t>ID:ZN0472</t>
+  </si>
+  <si>
+    <t>deborah-milano</t>
+  </si>
+  <si>
+    <t>Deborah Milano</t>
+  </si>
+  <si>
+    <t>ID:ZN0473</t>
+  </si>
+  <si>
+    <t>moravo-seed</t>
+  </si>
+  <si>
+    <t>Moravo Seed</t>
+  </si>
+  <si>
+    <t>ID:ZN0474</t>
+  </si>
+  <si>
+    <t>nostalgie</t>
+  </si>
+  <si>
+    <t>NOSTALGIE</t>
+  </si>
+  <si>
+    <t>ID:ZN0477</t>
+  </si>
+  <si>
+    <t>burberry</t>
+  </si>
+  <si>
+    <t>Burberry</t>
   </si>
 </sst>
 </file>
@@ -8604,7 +8772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDB66AD-1FF0-4104-BCB9-E546CFC91809}">
-  <dimension ref="A1:C870"/>
+  <dimension ref="A1:C889"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -18182,6 +18350,215 @@
         <v>2568</v>
       </c>
     </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C871" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B872" t="s">
+        <v>2578</v>
+      </c>
+      <c r="C872" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B873" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C873" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B874" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C874" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C875" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B876" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C876" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C877" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B878" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C878" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C879" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B880" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C880" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A881" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C881" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A882" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B882" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C882" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A883" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C883" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A884" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B884" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C884" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A885" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C885" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A886" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B886" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C886" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A887" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C887" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A888" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B888" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C888" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A889" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C889" t="s">
+        <v>2629</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/vazby_znacek.xlsx
+++ b/vazby_znacek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petr.hirsal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petr.hirsal\Desktop\dlazdice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56072468-8BD2-494E-A85C-45D99A339258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C38C7E-598E-47E1-BA55-D9B69E072BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
+    <workbookView xWindow="-28920" yWindow="180" windowWidth="29040" windowHeight="15720" xr2:uid="{DEEF875A-C45B-474B-908C-61CEEFA8F98C}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="2630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="2628">
   <si>
     <t>name</t>
   </si>
@@ -5603,13 +5603,7 @@
     <t>eggo</t>
   </si>
   <si>
-    <t>ID:ZN0251</t>
-  </si>
-  <si>
     <t>L'Oreal Paris</t>
-  </si>
-  <si>
-    <t>l-oreal-paris-1</t>
   </si>
   <si>
     <t>ID:ZN0250</t>
@@ -8782,7 +8776,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -9217,7 +9211,7 @@
         <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -9536,7 +9530,7 @@
         <v>199</v>
       </c>
       <c r="C69" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -9569,7 +9563,7 @@
         <v>208</v>
       </c>
       <c r="C72" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -9602,7 +9596,7 @@
         <v>211</v>
       </c>
       <c r="C75" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -9657,7 +9651,7 @@
         <v>226</v>
       </c>
       <c r="C80" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -10097,7 +10091,7 @@
         <v>342</v>
       </c>
       <c r="C120" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -10130,7 +10124,7 @@
         <v>348</v>
       </c>
       <c r="C123" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -10625,7 +10619,7 @@
         <v>479</v>
       </c>
       <c r="C168" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -12033,7 +12027,7 @@
         <v>859</v>
       </c>
       <c r="C296" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -12286,7 +12280,7 @@
         <v>922</v>
       </c>
       <c r="C319" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -12638,7 +12632,7 @@
         <v>1015</v>
       </c>
       <c r="C351" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -14717,7 +14711,7 @@
         <v>1582</v>
       </c>
       <c r="C540" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -14728,7 +14722,7 @@
         <v>1582</v>
       </c>
       <c r="C541" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -15745,2639 +15739,2639 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
+        <v>35</v>
+      </c>
+      <c r="B634" t="s">
+        <v>37</v>
+      </c>
+      <c r="C634" t="s">
         <v>1855</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B635" t="s">
         <v>1858</v>
       </c>
-      <c r="B635" t="s">
-        <v>1860</v>
-      </c>
       <c r="C635" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B636" t="s">
         <v>1861</v>
       </c>
-      <c r="B636" t="s">
-        <v>1863</v>
-      </c>
       <c r="C636" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B637" t="s">
         <v>1864</v>
       </c>
-      <c r="B637" t="s">
-        <v>1866</v>
-      </c>
       <c r="C637" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B638" t="s">
         <v>1867</v>
       </c>
-      <c r="B638" t="s">
-        <v>1869</v>
-      </c>
       <c r="C638" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B639" t="s">
         <v>1870</v>
       </c>
-      <c r="B639" t="s">
-        <v>1872</v>
-      </c>
       <c r="C639" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B640" t="s">
         <v>1870</v>
       </c>
-      <c r="B640" t="s">
-        <v>1872</v>
-      </c>
       <c r="C640" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B641" t="s">
         <v>1873</v>
       </c>
-      <c r="B641" t="s">
-        <v>1875</v>
-      </c>
       <c r="C641" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B642" t="s">
         <v>1876</v>
       </c>
-      <c r="B642" t="s">
-        <v>1878</v>
-      </c>
       <c r="C642" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B643" t="s">
         <v>1879</v>
       </c>
-      <c r="B643" t="s">
-        <v>1881</v>
-      </c>
       <c r="C643" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B644" t="s">
         <v>1882</v>
       </c>
-      <c r="B644" t="s">
-        <v>1884</v>
-      </c>
       <c r="C644" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B645" t="s">
         <v>1885</v>
       </c>
-      <c r="B645" t="s">
-        <v>1887</v>
-      </c>
       <c r="C645" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B646" t="s">
         <v>1888</v>
       </c>
-      <c r="B646" t="s">
-        <v>1890</v>
-      </c>
       <c r="C646" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B647" t="s">
         <v>1891</v>
       </c>
-      <c r="B647" t="s">
-        <v>1893</v>
-      </c>
       <c r="C647" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B648" t="s">
         <v>1894</v>
       </c>
-      <c r="B648" t="s">
-        <v>1896</v>
-      </c>
       <c r="C648" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B649" t="s">
         <v>1897</v>
       </c>
-      <c r="B649" t="s">
-        <v>1899</v>
-      </c>
       <c r="C649" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B650" t="s">
         <v>1900</v>
       </c>
-      <c r="B650" t="s">
-        <v>1902</v>
-      </c>
       <c r="C650" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B651" t="s">
         <v>1903</v>
       </c>
-      <c r="B651" t="s">
-        <v>1905</v>
-      </c>
       <c r="C651" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B652" t="s">
         <v>1906</v>
       </c>
-      <c r="B652" t="s">
-        <v>1908</v>
-      </c>
       <c r="C652" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B653" t="s">
         <v>1909</v>
       </c>
-      <c r="B653" t="s">
-        <v>1911</v>
-      </c>
       <c r="C653" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B654" t="s">
         <v>1912</v>
       </c>
-      <c r="B654" t="s">
-        <v>1914</v>
-      </c>
       <c r="C654" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B655" t="s">
         <v>1915</v>
       </c>
-      <c r="B655" t="s">
-        <v>1917</v>
-      </c>
       <c r="C655" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B656" t="s">
         <v>1918</v>
       </c>
-      <c r="B656" t="s">
-        <v>1920</v>
-      </c>
       <c r="C656" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B657" t="s">
         <v>1921</v>
       </c>
-      <c r="B657" t="s">
-        <v>1923</v>
-      </c>
       <c r="C657" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B658" t="s">
         <v>1924</v>
       </c>
-      <c r="B658" t="s">
-        <v>1926</v>
-      </c>
       <c r="C658" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B659" t="s">
         <v>1927</v>
       </c>
-      <c r="B659" t="s">
-        <v>1929</v>
-      </c>
       <c r="C659" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B660" t="s">
         <v>1930</v>
       </c>
-      <c r="B660" t="s">
-        <v>1932</v>
-      </c>
       <c r="C660" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B661" t="s">
         <v>1933</v>
       </c>
-      <c r="B661" t="s">
-        <v>1935</v>
-      </c>
       <c r="C661" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B662" t="s">
         <v>1936</v>
       </c>
-      <c r="B662" t="s">
-        <v>1938</v>
-      </c>
       <c r="C662" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B663" t="s">
         <v>1939</v>
       </c>
-      <c r="B663" t="s">
-        <v>1941</v>
-      </c>
       <c r="C663" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B664" t="s">
         <v>1942</v>
       </c>
-      <c r="B664" t="s">
-        <v>1944</v>
-      </c>
       <c r="C664" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B665" t="s">
         <v>1945</v>
       </c>
-      <c r="B665" t="s">
-        <v>1947</v>
-      </c>
       <c r="C665" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B666" t="s">
         <v>1948</v>
       </c>
-      <c r="B666" t="s">
-        <v>1950</v>
-      </c>
       <c r="C666" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B667" t="s">
         <v>1951</v>
       </c>
-      <c r="B667" t="s">
-        <v>1953</v>
-      </c>
       <c r="C667" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B668" t="s">
         <v>1954</v>
       </c>
-      <c r="B668" t="s">
-        <v>1956</v>
-      </c>
       <c r="C668" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B669" t="s">
         <v>1957</v>
       </c>
-      <c r="B669" t="s">
-        <v>1959</v>
-      </c>
       <c r="C669" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B670" t="s">
         <v>1960</v>
       </c>
-      <c r="B670" t="s">
-        <v>1962</v>
-      </c>
       <c r="C670" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B671" t="s">
         <v>1963</v>
       </c>
-      <c r="B671" t="s">
-        <v>1965</v>
-      </c>
       <c r="C671" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B672" t="s">
         <v>1966</v>
       </c>
-      <c r="B672" t="s">
-        <v>1968</v>
-      </c>
       <c r="C672" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B673" t="s">
         <v>1969</v>
       </c>
-      <c r="B673" t="s">
-        <v>1971</v>
-      </c>
       <c r="C673" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B674" t="s">
         <v>1972</v>
       </c>
-      <c r="B674" t="s">
-        <v>1974</v>
-      </c>
       <c r="C674" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B675" t="s">
         <v>1975</v>
       </c>
-      <c r="B675" t="s">
-        <v>1977</v>
-      </c>
       <c r="C675" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B676" t="s">
         <v>1978</v>
       </c>
-      <c r="B676" t="s">
-        <v>1980</v>
-      </c>
       <c r="C676" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B677" t="s">
         <v>1981</v>
       </c>
-      <c r="B677" t="s">
-        <v>1983</v>
-      </c>
       <c r="C677" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B678" t="s">
         <v>1984</v>
       </c>
-      <c r="B678" t="s">
-        <v>1986</v>
-      </c>
       <c r="C678" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B679" t="s">
         <v>1987</v>
       </c>
-      <c r="B679" t="s">
-        <v>1989</v>
-      </c>
       <c r="C679" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B680" t="s">
         <v>1990</v>
       </c>
-      <c r="B680" t="s">
-        <v>1992</v>
-      </c>
       <c r="C680" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B681" t="s">
         <v>1993</v>
       </c>
-      <c r="B681" t="s">
-        <v>1995</v>
-      </c>
       <c r="C681" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B682" t="s">
         <v>1993</v>
       </c>
-      <c r="B682" t="s">
-        <v>1995</v>
-      </c>
       <c r="C682" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B683" t="s">
         <v>1996</v>
       </c>
-      <c r="B683" t="s">
-        <v>1998</v>
-      </c>
       <c r="C683" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B684" t="s">
         <v>1999</v>
       </c>
-      <c r="B684" t="s">
-        <v>2001</v>
-      </c>
       <c r="C684" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B685" t="s">
         <v>2002</v>
       </c>
-      <c r="B685" t="s">
-        <v>2004</v>
-      </c>
       <c r="C685" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B686" t="s">
         <v>2005</v>
       </c>
-      <c r="B686" t="s">
-        <v>2007</v>
-      </c>
       <c r="C686" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B687" t="s">
         <v>2008</v>
       </c>
-      <c r="B687" t="s">
-        <v>2010</v>
-      </c>
       <c r="C687" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B688" t="s">
         <v>2011</v>
       </c>
-      <c r="B688" t="s">
-        <v>2013</v>
-      </c>
       <c r="C688" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B689" t="s">
         <v>2014</v>
       </c>
-      <c r="B689" t="s">
-        <v>2016</v>
-      </c>
       <c r="C689" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B690" t="s">
         <v>2017</v>
       </c>
-      <c r="B690" t="s">
-        <v>2019</v>
-      </c>
       <c r="C690" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B691" t="s">
         <v>2020</v>
       </c>
-      <c r="B691" t="s">
-        <v>2022</v>
-      </c>
       <c r="C691" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B692" t="s">
         <v>2023</v>
       </c>
-      <c r="B692" t="s">
-        <v>2025</v>
-      </c>
       <c r="C692" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B693" t="s">
         <v>2026</v>
       </c>
-      <c r="B693" t="s">
-        <v>2028</v>
-      </c>
       <c r="C693" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B694" t="s">
         <v>2029</v>
       </c>
-      <c r="B694" t="s">
-        <v>2031</v>
-      </c>
       <c r="C694" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B695" t="s">
         <v>2032</v>
       </c>
-      <c r="B695" t="s">
-        <v>2034</v>
-      </c>
       <c r="C695" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B696" t="s">
         <v>2035</v>
       </c>
-      <c r="B696" t="s">
-        <v>2037</v>
-      </c>
       <c r="C696" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B697" t="s">
         <v>2038</v>
       </c>
-      <c r="B697" t="s">
-        <v>2040</v>
-      </c>
       <c r="C697" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B698" t="s">
         <v>2041</v>
       </c>
-      <c r="B698" t="s">
-        <v>2043</v>
-      </c>
       <c r="C698" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B699" t="s">
         <v>2044</v>
       </c>
-      <c r="B699" t="s">
-        <v>2046</v>
-      </c>
       <c r="C699" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B700" t="s">
         <v>2047</v>
       </c>
-      <c r="B700" t="s">
-        <v>2049</v>
-      </c>
       <c r="C700" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B701" t="s">
         <v>2050</v>
       </c>
-      <c r="B701" t="s">
-        <v>2052</v>
-      </c>
       <c r="C701" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B702" t="s">
         <v>2053</v>
       </c>
-      <c r="B702" t="s">
-        <v>2055</v>
-      </c>
       <c r="C702" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B703" t="s">
         <v>2056</v>
       </c>
-      <c r="B703" t="s">
-        <v>2058</v>
-      </c>
       <c r="C703" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B704" t="s">
         <v>2059</v>
       </c>
-      <c r="B704" t="s">
-        <v>2061</v>
-      </c>
       <c r="C704" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B705" t="s">
         <v>2062</v>
       </c>
-      <c r="B705" t="s">
-        <v>2064</v>
-      </c>
       <c r="C705" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B706" t="s">
         <v>2065</v>
       </c>
-      <c r="B706" t="s">
-        <v>2067</v>
-      </c>
       <c r="C706" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B707" t="s">
         <v>2068</v>
       </c>
-      <c r="B707" t="s">
-        <v>2070</v>
-      </c>
       <c r="C707" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B708" t="s">
         <v>2071</v>
       </c>
-      <c r="B708" t="s">
-        <v>2073</v>
-      </c>
       <c r="C708" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B709" t="s">
         <v>2074</v>
       </c>
-      <c r="B709" t="s">
-        <v>2076</v>
-      </c>
       <c r="C709" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B710" t="s">
         <v>2077</v>
       </c>
-      <c r="B710" t="s">
-        <v>2079</v>
-      </c>
       <c r="C710" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B711" t="s">
         <v>2080</v>
       </c>
-      <c r="B711" t="s">
-        <v>2082</v>
-      </c>
       <c r="C711" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B712" t="s">
         <v>2083</v>
       </c>
-      <c r="B712" t="s">
-        <v>2085</v>
-      </c>
       <c r="C712" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B713" t="s">
         <v>2086</v>
       </c>
-      <c r="B713" t="s">
-        <v>2088</v>
-      </c>
       <c r="C713" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B714" t="s">
         <v>2089</v>
       </c>
-      <c r="B714" t="s">
-        <v>2091</v>
-      </c>
       <c r="C714" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B715" t="s">
         <v>2092</v>
       </c>
-      <c r="B715" t="s">
-        <v>2094</v>
-      </c>
       <c r="C715" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B716" t="s">
         <v>2095</v>
       </c>
-      <c r="B716" t="s">
-        <v>2097</v>
-      </c>
       <c r="C716" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B717" t="s">
         <v>2098</v>
       </c>
-      <c r="B717" t="s">
-        <v>2100</v>
-      </c>
       <c r="C717" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B718" t="s">
         <v>2101</v>
       </c>
-      <c r="B718" t="s">
-        <v>2103</v>
-      </c>
       <c r="C718" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B719" t="s">
         <v>2104</v>
       </c>
-      <c r="B719" t="s">
-        <v>2106</v>
-      </c>
       <c r="C719" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B720" t="s">
         <v>2107</v>
       </c>
-      <c r="B720" t="s">
-        <v>2109</v>
-      </c>
       <c r="C720" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B721" t="s">
         <v>2110</v>
       </c>
-      <c r="B721" t="s">
-        <v>2112</v>
-      </c>
       <c r="C721" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B722" t="s">
         <v>2113</v>
       </c>
-      <c r="B722" t="s">
-        <v>2115</v>
-      </c>
       <c r="C722" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B723" t="s">
         <v>2116</v>
       </c>
-      <c r="B723" t="s">
-        <v>2118</v>
-      </c>
       <c r="C723" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B724" t="s">
         <v>2119</v>
       </c>
-      <c r="B724" t="s">
-        <v>2121</v>
-      </c>
       <c r="C724" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B725" t="s">
         <v>2122</v>
       </c>
-      <c r="B725" t="s">
-        <v>2124</v>
-      </c>
       <c r="C725" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B726" t="s">
         <v>2125</v>
       </c>
-      <c r="B726" t="s">
-        <v>2127</v>
-      </c>
       <c r="C726" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B727" t="s">
         <v>2128</v>
       </c>
-      <c r="B727" t="s">
-        <v>2130</v>
-      </c>
       <c r="C727" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B728" t="s">
         <v>2131</v>
       </c>
-      <c r="B728" t="s">
-        <v>2133</v>
-      </c>
       <c r="C728" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B729" t="s">
         <v>2134</v>
       </c>
-      <c r="B729" t="s">
-        <v>2136</v>
-      </c>
       <c r="C729" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B730" t="s">
         <v>2137</v>
       </c>
-      <c r="B730" t="s">
-        <v>2139</v>
-      </c>
       <c r="C730" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B731" t="s">
         <v>2140</v>
       </c>
-      <c r="B731" t="s">
-        <v>2142</v>
-      </c>
       <c r="C731" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B732" t="s">
         <v>2143</v>
       </c>
-      <c r="B732" t="s">
-        <v>2145</v>
-      </c>
       <c r="C732" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B733" t="s">
         <v>2146</v>
       </c>
-      <c r="B733" t="s">
-        <v>2148</v>
-      </c>
       <c r="C733" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B734" t="s">
         <v>2149</v>
       </c>
-      <c r="B734" t="s">
-        <v>2151</v>
-      </c>
       <c r="C734" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B735" t="s">
         <v>2152</v>
       </c>
-      <c r="B735" t="s">
-        <v>2154</v>
-      </c>
       <c r="C735" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B736" t="s">
         <v>2155</v>
       </c>
-      <c r="B736" t="s">
-        <v>2157</v>
-      </c>
       <c r="C736" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B737" t="s">
         <v>2158</v>
       </c>
-      <c r="B737" t="s">
-        <v>2160</v>
-      </c>
       <c r="C737" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B738" t="s">
         <v>2161</v>
       </c>
-      <c r="B738" t="s">
-        <v>2163</v>
-      </c>
       <c r="C738" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B739" t="s">
         <v>2164</v>
       </c>
-      <c r="B739" t="s">
-        <v>2166</v>
-      </c>
       <c r="C739" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B740" t="s">
         <v>2167</v>
       </c>
-      <c r="B740" t="s">
-        <v>2169</v>
-      </c>
       <c r="C740" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B741" t="s">
         <v>2170</v>
       </c>
-      <c r="B741" t="s">
-        <v>2172</v>
-      </c>
       <c r="C741" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B742" t="s">
         <v>2173</v>
       </c>
-      <c r="B742" t="s">
-        <v>2175</v>
-      </c>
       <c r="C742" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B743" t="s">
         <v>2176</v>
       </c>
-      <c r="B743" t="s">
-        <v>2178</v>
-      </c>
       <c r="C743" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B744" t="s">
         <v>2179</v>
       </c>
-      <c r="B744" t="s">
-        <v>2181</v>
-      </c>
       <c r="C744" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B745" t="s">
         <v>2182</v>
       </c>
-      <c r="B745" t="s">
-        <v>2184</v>
-      </c>
       <c r="C745" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B746" t="s">
         <v>2185</v>
       </c>
-      <c r="B746" t="s">
-        <v>2187</v>
-      </c>
       <c r="C746" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B747" t="s">
         <v>2188</v>
       </c>
-      <c r="B747" t="s">
-        <v>2190</v>
-      </c>
       <c r="C747" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B748" t="s">
         <v>2191</v>
       </c>
-      <c r="B748" t="s">
-        <v>2193</v>
-      </c>
       <c r="C748" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B749" t="s">
         <v>2194</v>
       </c>
-      <c r="B749" t="s">
-        <v>2196</v>
-      </c>
       <c r="C749" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B750" t="s">
         <v>2197</v>
       </c>
-      <c r="B750" t="s">
-        <v>2199</v>
-      </c>
       <c r="C750" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B751" t="s">
         <v>2200</v>
       </c>
-      <c r="B751" t="s">
-        <v>2202</v>
-      </c>
       <c r="C751" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B752" t="s">
         <v>2203</v>
       </c>
-      <c r="B752" t="s">
-        <v>2205</v>
-      </c>
       <c r="C752" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B753" t="s">
         <v>2206</v>
       </c>
-      <c r="B753" t="s">
-        <v>2208</v>
-      </c>
       <c r="C753" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B754" t="s">
         <v>2209</v>
       </c>
-      <c r="B754" t="s">
-        <v>2211</v>
-      </c>
       <c r="C754" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B755" t="s">
         <v>2212</v>
       </c>
-      <c r="B755" t="s">
-        <v>2214</v>
-      </c>
       <c r="C755" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B756" t="s">
         <v>2215</v>
       </c>
-      <c r="B756" t="s">
-        <v>2217</v>
-      </c>
       <c r="C756" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B757" t="s">
         <v>2218</v>
       </c>
-      <c r="B757" t="s">
-        <v>2220</v>
-      </c>
       <c r="C757" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B758" t="s">
         <v>2221</v>
       </c>
-      <c r="B758" t="s">
-        <v>2223</v>
-      </c>
       <c r="C758" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B759" t="s">
         <v>2224</v>
       </c>
-      <c r="B759" t="s">
-        <v>2226</v>
-      </c>
       <c r="C759" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B760" t="s">
         <v>2227</v>
       </c>
-      <c r="B760" t="s">
-        <v>2229</v>
-      </c>
       <c r="C760" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B761" t="s">
         <v>2230</v>
       </c>
-      <c r="B761" t="s">
-        <v>2232</v>
-      </c>
       <c r="C761" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B762" t="s">
         <v>2233</v>
       </c>
-      <c r="B762" t="s">
-        <v>2235</v>
-      </c>
       <c r="C762" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B763" t="s">
         <v>2236</v>
       </c>
-      <c r="B763" t="s">
-        <v>2238</v>
-      </c>
       <c r="C763" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B764" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C764" t="s">
         <v>2263</v>
-      </c>
-      <c r="B764" t="s">
-        <v>2264</v>
-      </c>
-      <c r="C764" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B765" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C765" t="s">
         <v>2266</v>
-      </c>
-      <c r="B765" t="s">
-        <v>2267</v>
-      </c>
-      <c r="C765" t="s">
-        <v>2268</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B766" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C766" t="s">
         <v>2269</v>
-      </c>
-      <c r="B766" t="s">
-        <v>2270</v>
-      </c>
-      <c r="C766" t="s">
-        <v>2271</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B767" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C767" t="s">
         <v>2272</v>
-      </c>
-      <c r="B767" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C767" t="s">
-        <v>2274</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="B768" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="C768" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B769" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C769" t="s">
         <v>2245</v>
-      </c>
-      <c r="B769" t="s">
-        <v>2246</v>
-      </c>
-      <c r="C769" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="B770" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C770" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B771" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C771" t="s">
         <v>2242</v>
-      </c>
-      <c r="B771" t="s">
-        <v>2243</v>
-      </c>
-      <c r="C771" t="s">
-        <v>2244</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B772" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C772" t="s">
         <v>2276</v>
-      </c>
-      <c r="B772" t="s">
-        <v>2277</v>
-      </c>
-      <c r="C772" t="s">
-        <v>2278</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B773" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C773" t="s">
         <v>2248</v>
-      </c>
-      <c r="B773" t="s">
-        <v>2249</v>
-      </c>
-      <c r="C773" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B774" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C774" t="s">
         <v>2279</v>
-      </c>
-      <c r="B774" t="s">
-        <v>2280</v>
-      </c>
-      <c r="C774" t="s">
-        <v>2281</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B775" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C775" t="s">
         <v>2282</v>
-      </c>
-      <c r="B775" t="s">
-        <v>2283</v>
-      </c>
-      <c r="C775" t="s">
-        <v>2284</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="B776" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C776" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B777" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C777" t="s">
         <v>2285</v>
-      </c>
-      <c r="B777" t="s">
-        <v>2286</v>
-      </c>
-      <c r="C777" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B778" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C778" t="s">
         <v>2288</v>
-      </c>
-      <c r="B778" t="s">
-        <v>2289</v>
-      </c>
-      <c r="C778" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B779" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C779" t="s">
         <v>2291</v>
-      </c>
-      <c r="B779" t="s">
-        <v>2292</v>
-      </c>
-      <c r="C779" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B780" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C780" t="s">
         <v>2294</v>
-      </c>
-      <c r="B780" t="s">
-        <v>2295</v>
-      </c>
-      <c r="C780" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B781" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C781" t="s">
         <v>2297</v>
-      </c>
-      <c r="B781" t="s">
-        <v>2298</v>
-      </c>
-      <c r="C781" t="s">
-        <v>2299</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B782" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C782" t="s">
         <v>2300</v>
-      </c>
-      <c r="B782" t="s">
-        <v>2301</v>
-      </c>
-      <c r="C782" t="s">
-        <v>2302</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B783" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C783" t="s">
         <v>2303</v>
-      </c>
-      <c r="B783" t="s">
-        <v>2304</v>
-      </c>
-      <c r="C783" t="s">
-        <v>2305</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B784" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C784" t="s">
         <v>2306</v>
-      </c>
-      <c r="B784" t="s">
-        <v>2307</v>
-      </c>
-      <c r="C784" t="s">
-        <v>2308</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B785" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C785" t="s">
         <v>2309</v>
-      </c>
-      <c r="B785" t="s">
-        <v>2310</v>
-      </c>
-      <c r="C785" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B786" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C786" t="s">
         <v>2312</v>
-      </c>
-      <c r="B786" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C786" t="s">
-        <v>2314</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B787" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C787" t="s">
         <v>2315</v>
-      </c>
-      <c r="B787" t="s">
-        <v>2316</v>
-      </c>
-      <c r="C787" t="s">
-        <v>2317</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B788" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C788" t="s">
         <v>2318</v>
-      </c>
-      <c r="B788" t="s">
-        <v>2319</v>
-      </c>
-      <c r="C788" t="s">
-        <v>2320</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B789" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C789" t="s">
         <v>2321</v>
-      </c>
-      <c r="B789" t="s">
-        <v>2322</v>
-      </c>
-      <c r="C789" t="s">
-        <v>2323</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B790" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C790" t="s">
         <v>2324</v>
-      </c>
-      <c r="B790" t="s">
-        <v>2325</v>
-      </c>
-      <c r="C790" t="s">
-        <v>2326</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B791" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C791" t="s">
         <v>2327</v>
-      </c>
-      <c r="B791" t="s">
-        <v>2328</v>
-      </c>
-      <c r="C791" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B792" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C792" t="s">
         <v>2330</v>
-      </c>
-      <c r="B792" t="s">
-        <v>2331</v>
-      </c>
-      <c r="C792" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B793" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C793" t="s">
         <v>2333</v>
-      </c>
-      <c r="B793" t="s">
-        <v>2334</v>
-      </c>
-      <c r="C793" t="s">
-        <v>2335</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B794" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C794" t="s">
         <v>2336</v>
-      </c>
-      <c r="B794" t="s">
-        <v>2337</v>
-      </c>
-      <c r="C794" t="s">
-        <v>2338</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B795" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C795" t="s">
         <v>2339</v>
-      </c>
-      <c r="B795" t="s">
-        <v>2340</v>
-      </c>
-      <c r="C795" t="s">
-        <v>2341</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="B796" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C796" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="B797" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="C797" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B798" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C798" t="s">
         <v>2342</v>
-      </c>
-      <c r="B798" t="s">
-        <v>2343</v>
-      </c>
-      <c r="C798" t="s">
-        <v>2344</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B799" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C799" t="s">
         <v>2345</v>
-      </c>
-      <c r="B799" t="s">
-        <v>2346</v>
-      </c>
-      <c r="C799" t="s">
-        <v>2347</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B800" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C800" t="s">
         <v>2348</v>
-      </c>
-      <c r="B800" t="s">
-        <v>2349</v>
-      </c>
-      <c r="C800" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B801" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C801" t="s">
         <v>2351</v>
-      </c>
-      <c r="B801" t="s">
-        <v>2352</v>
-      </c>
-      <c r="C801" t="s">
-        <v>2353</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B802" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C802" t="s">
         <v>2354</v>
-      </c>
-      <c r="B802" t="s">
-        <v>2355</v>
-      </c>
-      <c r="C802" t="s">
-        <v>2356</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B803" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C803" t="s">
         <v>2357</v>
-      </c>
-      <c r="B803" t="s">
-        <v>2358</v>
-      </c>
-      <c r="C803" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B804" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C804" t="s">
         <v>2360</v>
-      </c>
-      <c r="B804" t="s">
-        <v>2361</v>
-      </c>
-      <c r="C804" t="s">
-        <v>2362</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B805" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C805" t="s">
         <v>2363</v>
-      </c>
-      <c r="B805" t="s">
-        <v>2364</v>
-      </c>
-      <c r="C805" t="s">
-        <v>2365</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B806" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C806" t="s">
         <v>2366</v>
-      </c>
-      <c r="B806" t="s">
-        <v>2367</v>
-      </c>
-      <c r="C806" t="s">
-        <v>2368</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B807" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C807" t="s">
         <v>2369</v>
-      </c>
-      <c r="B807" t="s">
-        <v>2370</v>
-      </c>
-      <c r="C807" t="s">
-        <v>2371</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B808" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C808" t="s">
         <v>2372</v>
-      </c>
-      <c r="B808" t="s">
-        <v>2373</v>
-      </c>
-      <c r="C808" t="s">
-        <v>2374</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B809" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C809" t="s">
         <v>2375</v>
-      </c>
-      <c r="B809" t="s">
-        <v>2376</v>
-      </c>
-      <c r="C809" t="s">
-        <v>2377</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B810" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C810" t="s">
         <v>2378</v>
-      </c>
-      <c r="B810" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C810" t="s">
-        <v>2380</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B811" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C811" t="s">
         <v>2381</v>
-      </c>
-      <c r="B811" t="s">
-        <v>2382</v>
-      </c>
-      <c r="C811" t="s">
-        <v>2383</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B812" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C812" t="s">
         <v>2384</v>
-      </c>
-      <c r="B812" t="s">
-        <v>2385</v>
-      </c>
-      <c r="C812" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B813" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C813" t="s">
         <v>2387</v>
-      </c>
-      <c r="B813" t="s">
-        <v>2388</v>
-      </c>
-      <c r="C813" t="s">
-        <v>2389</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B814" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C814" t="s">
         <v>2390</v>
-      </c>
-      <c r="B814" t="s">
-        <v>2391</v>
-      </c>
-      <c r="C814" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B815" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C815" t="s">
         <v>2393</v>
-      </c>
-      <c r="B815" t="s">
-        <v>2394</v>
-      </c>
-      <c r="C815" t="s">
-        <v>2395</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B816" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C816" t="s">
         <v>2396</v>
-      </c>
-      <c r="B816" t="s">
-        <v>2397</v>
-      </c>
-      <c r="C816" t="s">
-        <v>2398</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="B817" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C817" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B818" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C818" t="s">
         <v>2411</v>
-      </c>
-      <c r="B818" t="s">
-        <v>2412</v>
-      </c>
-      <c r="C818" t="s">
-        <v>2413</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B819" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C819" t="s">
         <v>2414</v>
-      </c>
-      <c r="B819" t="s">
-        <v>2415</v>
-      </c>
-      <c r="C819" t="s">
-        <v>2416</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B820" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C820" t="s">
         <v>2417</v>
-      </c>
-      <c r="B820" t="s">
-        <v>2418</v>
-      </c>
-      <c r="C820" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B821" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C821" t="s">
         <v>2420</v>
-      </c>
-      <c r="B821" t="s">
-        <v>2421</v>
-      </c>
-      <c r="C821" t="s">
-        <v>2422</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B822" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C822" t="s">
         <v>2423</v>
-      </c>
-      <c r="B822" t="s">
-        <v>2424</v>
-      </c>
-      <c r="C822" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B823" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C823" t="s">
         <v>2426</v>
-      </c>
-      <c r="B823" t="s">
-        <v>2427</v>
-      </c>
-      <c r="C823" t="s">
-        <v>2428</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B824" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C824" t="s">
         <v>2429</v>
-      </c>
-      <c r="B824" t="s">
-        <v>2430</v>
-      </c>
-      <c r="C824" t="s">
-        <v>2431</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B825" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C825" t="s">
         <v>2432</v>
-      </c>
-      <c r="B825" t="s">
-        <v>2433</v>
-      </c>
-      <c r="C825" t="s">
-        <v>2434</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B826" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C826" t="s">
         <v>2435</v>
-      </c>
-      <c r="B826" t="s">
-        <v>2436</v>
-      </c>
-      <c r="C826" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B827" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C827" t="s">
         <v>2438</v>
-      </c>
-      <c r="B827" t="s">
-        <v>2439</v>
-      </c>
-      <c r="C827" t="s">
-        <v>2440</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B828" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C828" t="s">
         <v>2441</v>
-      </c>
-      <c r="B828" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C828" t="s">
-        <v>2443</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B829" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C829" t="s">
         <v>2444</v>
-      </c>
-      <c r="B829" t="s">
-        <v>2445</v>
-      </c>
-      <c r="C829" t="s">
-        <v>2446</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B830" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C830" t="s">
         <v>2447</v>
-      </c>
-      <c r="B830" t="s">
-        <v>2448</v>
-      </c>
-      <c r="C830" t="s">
-        <v>2449</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B831" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C831" t="s">
         <v>2450</v>
-      </c>
-      <c r="B831" t="s">
-        <v>2451</v>
-      </c>
-      <c r="C831" t="s">
-        <v>2452</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B832" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C832" t="s">
         <v>2453</v>
-      </c>
-      <c r="B832" t="s">
-        <v>2454</v>
-      </c>
-      <c r="C832" t="s">
-        <v>2455</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B833" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C833" t="s">
         <v>2456</v>
-      </c>
-      <c r="B833" t="s">
-        <v>2457</v>
-      </c>
-      <c r="C833" t="s">
-        <v>2458</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B834" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C834" t="s">
         <v>2459</v>
-      </c>
-      <c r="B834" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C834" t="s">
-        <v>2461</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B835" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C835" t="s">
         <v>2462</v>
-      </c>
-      <c r="B835" t="s">
-        <v>2463</v>
-      </c>
-      <c r="C835" t="s">
-        <v>2464</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B836" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C836" t="s">
         <v>2465</v>
-      </c>
-      <c r="B836" t="s">
-        <v>2466</v>
-      </c>
-      <c r="C836" t="s">
-        <v>2467</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B837" t="s">
+        <v>2467</v>
+      </c>
+      <c r="C837" t="s">
         <v>2468</v>
-      </c>
-      <c r="B837" t="s">
-        <v>2469</v>
-      </c>
-      <c r="C837" t="s">
-        <v>2470</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="B838" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="C838" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B839" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C839" t="s">
         <v>2473</v>
-      </c>
-      <c r="B839" t="s">
-        <v>2474</v>
-      </c>
-      <c r="C839" t="s">
-        <v>2475</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B840" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C840" t="s">
         <v>2476</v>
-      </c>
-      <c r="B840" t="s">
-        <v>2477</v>
-      </c>
-      <c r="C840" t="s">
-        <v>2478</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B841" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C841" t="s">
         <v>2479</v>
-      </c>
-      <c r="B841" t="s">
-        <v>2480</v>
-      </c>
-      <c r="C841" t="s">
-        <v>2481</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B842" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C842" t="s">
         <v>2482</v>
-      </c>
-      <c r="B842" t="s">
-        <v>2483</v>
-      </c>
-      <c r="C842" t="s">
-        <v>2484</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B843" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C843" t="s">
         <v>2485</v>
-      </c>
-      <c r="B843" t="s">
-        <v>2486</v>
-      </c>
-      <c r="C843" t="s">
-        <v>2487</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B844" t="s">
+        <v>2487</v>
+      </c>
+      <c r="C844" t="s">
         <v>2488</v>
-      </c>
-      <c r="B844" t="s">
-        <v>2489</v>
-      </c>
-      <c r="C844" t="s">
-        <v>2490</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B845" t="s">
+        <v>2490</v>
+      </c>
+      <c r="C845" t="s">
         <v>2491</v>
-      </c>
-      <c r="B845" t="s">
-        <v>2492</v>
-      </c>
-      <c r="C845" t="s">
-        <v>2493</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B846" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C846" t="s">
         <v>2494</v>
-      </c>
-      <c r="B846" t="s">
-        <v>2495</v>
-      </c>
-      <c r="C846" t="s">
-        <v>2496</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B847" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C847" t="s">
         <v>2497</v>
-      </c>
-      <c r="B847" t="s">
-        <v>2498</v>
-      </c>
-      <c r="C847" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B848" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C848" t="s">
         <v>2500</v>
-      </c>
-      <c r="B848" t="s">
-        <v>2501</v>
-      </c>
-      <c r="C848" t="s">
-        <v>2502</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B849" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C849" t="s">
         <v>2503</v>
-      </c>
-      <c r="B849" t="s">
-        <v>2504</v>
-      </c>
-      <c r="C849" t="s">
-        <v>2505</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B850" t="s">
+        <v>2505</v>
+      </c>
+      <c r="C850" t="s">
         <v>2506</v>
-      </c>
-      <c r="B850" t="s">
-        <v>2507</v>
-      </c>
-      <c r="C850" t="s">
-        <v>2508</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B851" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C851" t="s">
         <v>2509</v>
-      </c>
-      <c r="B851" t="s">
-        <v>2510</v>
-      </c>
-      <c r="C851" t="s">
-        <v>2511</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B852" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C852" t="s">
         <v>2512</v>
-      </c>
-      <c r="B852" t="s">
-        <v>2513</v>
-      </c>
-      <c r="C852" t="s">
-        <v>2514</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B853" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C853" t="s">
         <v>2515</v>
-      </c>
-      <c r="B853" t="s">
-        <v>2516</v>
-      </c>
-      <c r="C853" t="s">
-        <v>2517</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B854" t="s">
+        <v>2517</v>
+      </c>
+      <c r="C854" t="s">
         <v>2518</v>
-      </c>
-      <c r="B854" t="s">
-        <v>2519</v>
-      </c>
-      <c r="C854" t="s">
-        <v>2520</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B855" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C855" t="s">
         <v>2521</v>
-      </c>
-      <c r="B855" t="s">
-        <v>2522</v>
-      </c>
-      <c r="C855" t="s">
-        <v>2523</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B856" t="s">
+        <v>2523</v>
+      </c>
+      <c r="C856" t="s">
         <v>2524</v>
-      </c>
-      <c r="B856" t="s">
-        <v>2525</v>
-      </c>
-      <c r="C856" t="s">
-        <v>2526</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B857" t="s">
+        <v>2526</v>
+      </c>
+      <c r="C857" t="s">
         <v>2527</v>
-      </c>
-      <c r="B857" t="s">
-        <v>2528</v>
-      </c>
-      <c r="C857" t="s">
-        <v>2529</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B858" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C858" t="s">
         <v>2530</v>
-      </c>
-      <c r="B858" t="s">
-        <v>2531</v>
-      </c>
-      <c r="C858" t="s">
-        <v>2532</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B859" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C859" t="s">
         <v>2533</v>
-      </c>
-      <c r="B859" t="s">
-        <v>2534</v>
-      </c>
-      <c r="C859" t="s">
-        <v>2535</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B860" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C860" t="s">
         <v>2536</v>
-      </c>
-      <c r="B860" t="s">
-        <v>2537</v>
-      </c>
-      <c r="C860" t="s">
-        <v>2538</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B861" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C861" t="s">
         <v>2539</v>
-      </c>
-      <c r="B861" t="s">
-        <v>2540</v>
-      </c>
-      <c r="C861" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B862" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C862" t="s">
         <v>2542</v>
-      </c>
-      <c r="B862" t="s">
-        <v>2543</v>
-      </c>
-      <c r="C862" t="s">
-        <v>2544</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B863" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C863" t="s">
         <v>2545</v>
-      </c>
-      <c r="B863" t="s">
-        <v>2546</v>
-      </c>
-      <c r="C863" t="s">
-        <v>2547</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B864" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C864" t="s">
         <v>2548</v>
-      </c>
-      <c r="B864" t="s">
-        <v>2549</v>
-      </c>
-      <c r="C864" t="s">
-        <v>2550</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C865" t="s">
         <v>2551</v>
-      </c>
-      <c r="B865" t="s">
-        <v>2552</v>
-      </c>
-      <c r="C865" t="s">
-        <v>2553</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B866" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C866" t="s">
         <v>2554</v>
-      </c>
-      <c r="B866" t="s">
-        <v>2555</v>
-      </c>
-      <c r="C866" t="s">
-        <v>2556</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C867" t="s">
         <v>2557</v>
-      </c>
-      <c r="B867" t="s">
-        <v>2558</v>
-      </c>
-      <c r="C867" t="s">
-        <v>2559</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B868" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C868" t="s">
         <v>2560</v>
-      </c>
-      <c r="B868" t="s">
-        <v>2561</v>
-      </c>
-      <c r="C868" t="s">
-        <v>2562</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C869" t="s">
         <v>2563</v>
-      </c>
-      <c r="B869" t="s">
-        <v>2564</v>
-      </c>
-      <c r="C869" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B870" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C870" t="s">
         <v>2566</v>
-      </c>
-      <c r="B870" t="s">
-        <v>2567</v>
-      </c>
-      <c r="C870" t="s">
-        <v>2568</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C871" t="s">
         <v>2574</v>
-      </c>
-      <c r="B871" t="s">
-        <v>2575</v>
-      </c>
-      <c r="C871" t="s">
-        <v>2576</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B872" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C872" t="s">
         <v>2577</v>
-      </c>
-      <c r="B872" t="s">
-        <v>2578</v>
-      </c>
-      <c r="C872" t="s">
-        <v>2579</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="B873" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="C873" t="s">
         <v>1572</v>
@@ -18385,178 +18379,178 @@
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B874" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C874" t="s">
         <v>2582</v>
-      </c>
-      <c r="B874" t="s">
-        <v>2583</v>
-      </c>
-      <c r="C874" t="s">
-        <v>2584</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C875" t="s">
         <v>2585</v>
-      </c>
-      <c r="B875" t="s">
-        <v>2586</v>
-      </c>
-      <c r="C875" t="s">
-        <v>2587</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B876" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C876" t="s">
         <v>2588</v>
-      </c>
-      <c r="B876" t="s">
-        <v>2589</v>
-      </c>
-      <c r="C876" t="s">
-        <v>2590</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C877" t="s">
         <v>2591</v>
-      </c>
-      <c r="B877" t="s">
-        <v>2592</v>
-      </c>
-      <c r="C877" t="s">
-        <v>2593</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B878" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C878" t="s">
         <v>2594</v>
-      </c>
-      <c r="B878" t="s">
-        <v>2595</v>
-      </c>
-      <c r="C878" t="s">
-        <v>2596</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C879" t="s">
         <v>2597</v>
-      </c>
-      <c r="B879" t="s">
-        <v>2598</v>
-      </c>
-      <c r="C879" t="s">
-        <v>2599</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B880" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C880" t="s">
         <v>2600</v>
-      </c>
-      <c r="B880" t="s">
-        <v>2601</v>
-      </c>
-      <c r="C880" t="s">
-        <v>2602</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C881" t="s">
         <v>2603</v>
-      </c>
-      <c r="B881" t="s">
-        <v>2604</v>
-      </c>
-      <c r="C881" t="s">
-        <v>2605</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B882" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C882" t="s">
         <v>2606</v>
-      </c>
-      <c r="B882" t="s">
-        <v>2607</v>
-      </c>
-      <c r="C882" t="s">
-        <v>2608</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C883" t="s">
         <v>2609</v>
-      </c>
-      <c r="B883" t="s">
-        <v>2610</v>
-      </c>
-      <c r="C883" t="s">
-        <v>2611</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B884" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C884" t="s">
         <v>2612</v>
-      </c>
-      <c r="B884" t="s">
-        <v>2613</v>
-      </c>
-      <c r="C884" t="s">
-        <v>2614</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C885" t="s">
         <v>2615</v>
-      </c>
-      <c r="B885" t="s">
-        <v>2616</v>
-      </c>
-      <c r="C885" t="s">
-        <v>2617</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B886" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C886" t="s">
         <v>2618</v>
-      </c>
-      <c r="B886" t="s">
-        <v>2619</v>
-      </c>
-      <c r="C886" t="s">
-        <v>2620</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C887" t="s">
         <v>2621</v>
-      </c>
-      <c r="B887" t="s">
-        <v>2622</v>
-      </c>
-      <c r="C887" t="s">
-        <v>2623</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B888" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C888" t="s">
         <v>2624</v>
-      </c>
-      <c r="B888" t="s">
-        <v>2625</v>
-      </c>
-      <c r="C888" t="s">
-        <v>2626</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C889" t="s">
         <v>2627</v>
-      </c>
-      <c r="B889" t="s">
-        <v>2628</v>
-      </c>
-      <c r="C889" t="s">
-        <v>2629</v>
       </c>
     </row>
   </sheetData>
